--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,6 +988,658 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130331828</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75286</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Slerebosjön, 200 m Ö om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>344522</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6433359</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130331860</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Slerebosjön, 200 m Ö om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>344517</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6433262</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130331824</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97541</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Slerebosjön, 200 m Ö om, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>344482</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6433360</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130331837</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75286</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Slerebosjön, 200 m Ö om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>344534</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6433351</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130331874</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83150</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>308</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Slerebosjön, 200 m Ö om, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>344531</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6433318</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130331854</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75286</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slerebosjön, 200 m Ö om, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>344499</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6433329</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>130331828</v>
       </c>
       <c r="B5" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130331860</v>
       </c>
       <c r="B6" t="n">
-        <v>83141</v>
+        <v>83144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>130331824</v>
       </c>
       <c r="B7" t="n">
-        <v>97541</v>
+        <v>97544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>130331837</v>
       </c>
       <c r="B8" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>130331874</v>
       </c>
       <c r="B9" t="n">
-        <v>83150</v>
+        <v>83153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>130331854</v>
       </c>
       <c r="B10" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130318035</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>130318036</v>
       </c>
       <c r="B3" t="n">
-        <v>57820</v>
+        <v>57846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>130318028</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130331828</v>
       </c>
       <c r="B5" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130331860</v>
       </c>
       <c r="B6" t="n">
-        <v>83144</v>
+        <v>83170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>130331824</v>
       </c>
       <c r="B7" t="n">
-        <v>97544</v>
+        <v>97570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>130331837</v>
       </c>
       <c r="B8" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>130331874</v>
       </c>
       <c r="B9" t="n">
-        <v>83153</v>
+        <v>83179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>130331854</v>
       </c>
       <c r="B10" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>130536439</v>
       </c>
       <c r="B12" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>130536468</v>
       </c>
       <c r="B13" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>130536318</v>
       </c>
       <c r="B14" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -1109,7 +1109,7 @@
         <v>130331860</v>
       </c>
       <c r="B6" t="n">
-        <v>83170</v>
+        <v>83171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>130331824</v>
       </c>
       <c r="B7" t="n">
-        <v>97570</v>
+        <v>97571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>130331874</v>
       </c>
       <c r="B9" t="n">
-        <v>83179</v>
+        <v>83180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -1109,7 +1109,7 @@
         <v>130331860</v>
       </c>
       <c r="B6" t="n">
-        <v>83171</v>
+        <v>83172</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>130331824</v>
       </c>
       <c r="B7" t="n">
-        <v>97571</v>
+        <v>97572</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>130331874</v>
       </c>
       <c r="B9" t="n">
-        <v>83180</v>
+        <v>83181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130318035</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>130318036</v>
       </c>
       <c r="B3" t="n">
-        <v>57846</v>
+        <v>57848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>130318028</v>
       </c>
       <c r="B4" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130331828</v>
       </c>
       <c r="B5" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130331860</v>
       </c>
       <c r="B6" t="n">
-        <v>83172</v>
+        <v>83174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>130331824</v>
       </c>
       <c r="B7" t="n">
-        <v>97572</v>
+        <v>97574</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>130331837</v>
       </c>
       <c r="B8" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>130331874</v>
       </c>
       <c r="B9" t="n">
-        <v>83181</v>
+        <v>83183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>130331854</v>
       </c>
       <c r="B10" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>130536439</v>
       </c>
       <c r="B12" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>130536468</v>
       </c>
       <c r="B13" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>130536318</v>
       </c>
       <c r="B14" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -1225,7 +1225,7 @@
         <v>130331824</v>
       </c>
       <c r="B7" t="n">
-        <v>97574</v>
+        <v>97578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130318035</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>130318036</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57856</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>130318028</v>
       </c>
       <c r="B4" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130331828</v>
       </c>
       <c r="B5" t="n">
-        <v>75317</v>
+        <v>75325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130331860</v>
       </c>
       <c r="B6" t="n">
-        <v>83174</v>
+        <v>83182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>130331824</v>
       </c>
       <c r="B7" t="n">
-        <v>97578</v>
+        <v>97591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>130331837</v>
       </c>
       <c r="B8" t="n">
-        <v>75317</v>
+        <v>75325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>130331874</v>
       </c>
       <c r="B9" t="n">
-        <v>83183</v>
+        <v>83191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>130331854</v>
       </c>
       <c r="B10" t="n">
-        <v>75317</v>
+        <v>75325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>130536439</v>
       </c>
       <c r="B12" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>130536468</v>
       </c>
       <c r="B13" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>130536318</v>
       </c>
       <c r="B14" t="n">
-        <v>75317</v>
+        <v>75325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130318035</v>
       </c>
       <c r="B2" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>130318036</v>
       </c>
       <c r="B3" t="n">
-        <v>57856</v>
+        <v>57857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>130318028</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130331828</v>
       </c>
       <c r="B5" t="n">
-        <v>75325</v>
+        <v>75326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130331860</v>
       </c>
       <c r="B6" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>130331824</v>
       </c>
       <c r="B7" t="n">
-        <v>97591</v>
+        <v>97592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>130331837</v>
       </c>
       <c r="B8" t="n">
-        <v>75325</v>
+        <v>75326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>130331874</v>
       </c>
       <c r="B9" t="n">
-        <v>83191</v>
+        <v>83192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>130331854</v>
       </c>
       <c r="B10" t="n">
-        <v>75325</v>
+        <v>75326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>130536439</v>
       </c>
       <c r="B12" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>130536468</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>130536318</v>
       </c>
       <c r="B14" t="n">
-        <v>75325</v>
+        <v>75326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,6 +2077,1402 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130827868</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>344488</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433273</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130827869</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75198</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>344518</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433262</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130827881</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>344495</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6433268</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130827880</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>344488</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6433273</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130827874</v>
+      </c>
+      <c r="B19" t="n">
+        <v>75326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>344473</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433342</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130827872</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58235</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>344461</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6433331</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130827867</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97592</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>344478</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6433317</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130827877</v>
+      </c>
+      <c r="B22" t="n">
+        <v>83183</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>344518</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6433262</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130827875</v>
+      </c>
+      <c r="B23" t="n">
+        <v>75326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>344478</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6433317</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130827870</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>344458</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6433350</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130827882</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>344503</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6433291</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130827876</v>
+      </c>
+      <c r="B26" t="n">
+        <v>75326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>344449</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6433318</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130827873</v>
+      </c>
+      <c r="B27" t="n">
+        <v>83185</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>306</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>344451</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6433334</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130318035</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>130318036</v>
       </c>
       <c r="B3" t="n">
-        <v>57857</v>
+        <v>57858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>130318028</v>
       </c>
       <c r="B4" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130331828</v>
+        <v>130331860</v>
       </c>
       <c r="B5" t="n">
-        <v>75326</v>
+        <v>83184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>344522</v>
+        <v>344517</v>
       </c>
       <c r="R5" t="n">
-        <v>6433359</v>
+        <v>6433262</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130331860</v>
+        <v>130331828</v>
       </c>
       <c r="B6" t="n">
-        <v>83183</v>
+        <v>75327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>344517</v>
+        <v>344522</v>
       </c>
       <c r="R6" t="n">
-        <v>6433262</v>
+        <v>6433359</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1225,7 @@
         <v>130331824</v>
       </c>
       <c r="B7" t="n">
-        <v>97592</v>
+        <v>97595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>130331837</v>
       </c>
       <c r="B8" t="n">
-        <v>75326</v>
+        <v>75327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>130331874</v>
       </c>
       <c r="B9" t="n">
-        <v>83192</v>
+        <v>83193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>130331854</v>
       </c>
       <c r="B10" t="n">
-        <v>75326</v>
+        <v>75327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>130536468</v>
       </c>
       <c r="B13" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>130536318</v>
       </c>
       <c r="B14" t="n">
-        <v>75326</v>
+        <v>75327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>130827869</v>
       </c>
       <c r="B16" t="n">
-        <v>75198</v>
+        <v>75199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>130827874</v>
       </c>
       <c r="B19" t="n">
-        <v>75326</v>
+        <v>75327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>130827872</v>
       </c>
       <c r="B20" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>130827867</v>
       </c>
       <c r="B21" t="n">
-        <v>97592</v>
+        <v>97595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>130827877</v>
       </c>
       <c r="B22" t="n">
-        <v>83183</v>
+        <v>83184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>130827875</v>
       </c>
       <c r="B23" t="n">
-        <v>75326</v>
+        <v>75327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130827876</v>
+        <v>130827873</v>
       </c>
       <c r="B26" t="n">
-        <v>75326</v>
+        <v>83186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>344449</v>
+        <v>344451</v>
       </c>
       <c r="R26" t="n">
-        <v>6433318</v>
+        <v>6433334</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130827873</v>
+        <v>130827876</v>
       </c>
       <c r="B27" t="n">
-        <v>83185</v>
+        <v>75327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3374,21 +3374,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>306</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>344451</v>
+        <v>344449</v>
       </c>
       <c r="R27" t="n">
-        <v>6433334</v>
+        <v>6433318</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130331860</v>
+        <v>130331828</v>
       </c>
       <c r="B5" t="n">
-        <v>83184</v>
+        <v>75327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>344517</v>
+        <v>344522</v>
       </c>
       <c r="R5" t="n">
-        <v>6433262</v>
+        <v>6433359</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130331828</v>
+        <v>130331860</v>
       </c>
       <c r="B6" t="n">
-        <v>75327</v>
+        <v>83184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>344522</v>
+        <v>344517</v>
       </c>
       <c r="R6" t="n">
-        <v>6433359</v>
+        <v>6433262</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 63239-2025 artfynd.xlsx
+++ b/artfynd/A 63239-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130827873</v>
+        <v>130827876</v>
       </c>
       <c r="B26" t="n">
-        <v>83186</v>
+        <v>75327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>306</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>344451</v>
+        <v>344449</v>
       </c>
       <c r="R26" t="n">
-        <v>6433334</v>
+        <v>6433318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130827876</v>
+        <v>130827873</v>
       </c>
       <c r="B27" t="n">
-        <v>75327</v>
+        <v>83186</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3374,21 +3374,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>344449</v>
+        <v>344451</v>
       </c>
       <c r="R27" t="n">
-        <v>6433318</v>
+        <v>6433334</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3472,6 +3472,241 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130918028</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>344470</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6433314</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130917555</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>344470</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6433314</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Sågs på nära håll.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
